--- a/business_forms/025_investment_readiness_assessment_form--business_forms.xlsx
+++ b/business_forms/025_investment_readiness_assessment_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'business_forms'}</t>
+          <t>business_forms</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Business Forms'}</t>
+          <t>Business Forms</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'seed_funding'}</t>
+          <t>seed_funding</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Seed Funding'}</t>
+          <t>Seed Funding</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'series_a'}</t>
+          <t>series_a</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Series A'}</t>
+          <t>Series A</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'series_b'}</t>
+          <t>series_b</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Series B'}</t>
+          <t>Series B</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'venture_capitalist'}</t>
+          <t>venture_capitalist</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Venture Capitalist'}</t>
+          <t>Venture Capitalist</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'angel_investor'}</t>
+          <t>angel_investor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Angel Investor'}</t>
+          <t>Angel Investor</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'venture_partner'}</t>
+          <t>venture_partner</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Venture Partner'}</t>
+          <t>Venture Partner</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'family_office'}</t>
+          <t>family_office</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Family Office'}</t>
+          <t>Family Office</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'1-5'}</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': '1-5'}</t>
+          <t>1-5</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'6-10'}</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': '6-10'}</t>
+          <t>6-10</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'11-20'}</t>
+          <t>11-20</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': '11-20'}</t>
+          <t>11-20</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'21-50'}</t>
+          <t>21-50</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': '21-50'}</t>
+          <t>21-50</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'more_than_50'}</t>
+          <t>more_than_50</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'More than 50'}</t>
+          <t>More than 50</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'less_than_$500,000'}</t>
+          <t>less_than_$500,000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Less than $500,000'}</t>
+          <t>Less than $500,000</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'$500,000_to_$2m'}</t>
+          <t>$500,000_to_$2m</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': '$500,000 to $2M'}</t>
+          <t>$500,000 to $2M</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'$2m_to_$5m'}</t>
+          <t>$2m_to_$5m</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': '$2M to $5M'}</t>
+          <t>$2M to $5M</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'$5m_to_$10m'}</t>
+          <t>$5m_to_$10m</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': '$5M to $10M'}</t>
+          <t>$5M to $10M</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'more_than_$10m'}</t>
+          <t>more_than_$10m</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'More than $10M'}</t>
+          <t>More than $10M</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'private_corporation'}</t>
+          <t>private_corporation</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Private Corporation'}</t>
+          <t>Private Corporation</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'partnership'}</t>
+          <t>partnership</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Partnership'}</t>
+          <t>Partnership</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'llc'}</t>
+          <t>llc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'LLC'}</t>
+          <t>LLC</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'non-profit'}</t>
+          <t>non-profit</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Non-Profit'}</t>
+          <t>Non-Profit</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'s-corp'}</t>
+          <t>s-corp</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'S-Corp'}</t>
+          <t>S-Corp</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'c-corp'}</t>
+          <t>c-corp</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'C-Corp'}</t>
+          <t>C-Corp</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'partnership'}</t>
+          <t>partnership</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Partnership'}</t>
+          <t>Partnership</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'sole_proprietorship'}</t>
+          <t>sole_proprietorship</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Sole Proprietorship'}</t>
+          <t>Sole Proprietorship</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'software_as_a_service_(saas)'}</t>
+          <t>software_as_a_service_(saas)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'Software as a Service (SaaS)'}</t>
+          <t>Software as a Service (SaaS)</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'e-commerce'}</t>
+          <t>e-commerce</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'E-commerce'}</t>
+          <t>E-commerce</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'healthcare_and_biotech'}</t>
+          <t>healthcare_and_biotech</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'Healthcare and Biotech'}</t>
+          <t>Healthcare and Biotech</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'finance_and_insurance'}</t>
+          <t>finance_and_insurance</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 'Finance and Insurance'}</t>
+          <t>Finance and Insurance</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_'usa'}</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 'USA'}</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_'canada'}</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 'Canada'}</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'signed'}</t>
+          <t>signed</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 'Signed'}</t>
+          <t>Signed</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_'unsigned'}</t>
+          <t>unsigned</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 'Unsigned'}</t>
+          <t>Unsigned</t>
         </is>
       </c>
     </row>
